--- a/Thesis Forecasting/metadata/rbfnn/validation_testing_summary.xlsx
+++ b/Thesis Forecasting/metadata/rbfnn/validation_testing_summary.xlsx
@@ -500,31 +500,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="D2" t="n">
-        <v>3.471231035467674</v>
+        <v>3.469709109951022</v>
       </c>
       <c r="E2" t="n">
-        <v>1.726776719652155</v>
+        <v>1.726094758945026</v>
       </c>
       <c r="F2" t="n">
-        <v>2.755809174796953</v>
+        <v>2.756650895208767</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9290627965976143</v>
+        <v>0.9290194565788212</v>
       </c>
       <c r="H2" t="n">
-        <v>3.475919113707131</v>
+        <v>3.476164999616764</v>
       </c>
       <c r="I2" t="n">
-        <v>1.840847984937388</v>
+        <v>1.841105299238234</v>
       </c>
       <c r="J2" t="n">
-        <v>3.440295102101322</v>
+        <v>3.440686379843341</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8988599585985897</v>
+        <v>0.8988369512132961</v>
       </c>
     </row>
     <row r="3">
@@ -539,19 +539,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D3" t="n">
-        <v>1.080237388266095</v>
+        <v>1.080237414062809</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9836404595910582</v>
+        <v>0.9836404855962289</v>
       </c>
       <c r="F3" t="n">
-        <v>4.296788174711516</v>
+        <v>4.296788179362019</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8217338979659277</v>
+        <v>0.8217338975800454</v>
       </c>
       <c r="H3" t="n">
         <v>1.372393407127368</v>
@@ -578,31 +578,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8267609583386537</v>
+        <v>0.8267609624278227</v>
       </c>
       <c r="E4" t="n">
-        <v>0.716515938221218</v>
+        <v>0.7165159423868309</v>
       </c>
       <c r="F4" t="n">
-        <v>3.362162388246943</v>
+        <v>3.362162393322077</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9528117569485496</v>
+        <v>0.9528117568060896</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6106872916793786</v>
+        <v>0.6106872916782813</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6974508930056273</v>
+        <v>0.6974508930041152</v>
       </c>
       <c r="J4" t="n">
-        <v>3.077447039614186</v>
+        <v>3.07744703961429</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9453153141242143</v>
+        <v>0.9453153141242105</v>
       </c>
     </row>
     <row r="5">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D5" t="n">
-        <v>4.090822638647039</v>
+        <v>4.090822638847586</v>
       </c>
       <c r="E5" t="n">
-        <v>1.469152401165102</v>
+        <v>1.469152401234568</v>
       </c>
       <c r="F5" t="n">
-        <v>2.231269481513257</v>
+        <v>2.231269481635627</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9043404627666414</v>
+        <v>0.9043404627561488</v>
       </c>
       <c r="H5" t="n">
         <v>4.039603029011061</v>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>2.412584472589698</v>
+        <v>2.41258447264652</v>
       </c>
       <c r="E6" t="n">
-        <v>3.667330521179721</v>
+        <v>3.667330521262003</v>
       </c>
       <c r="F6" t="n">
-        <v>7.981140072128379</v>
+        <v>7.981140072098497</v>
       </c>
       <c r="G6" t="n">
-        <v>0.83490126947832</v>
+        <v>0.8349012694795562</v>
       </c>
       <c r="H6" t="n">
         <v>1.404527208907398</v>
@@ -695,31 +695,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D7" t="n">
-        <v>3.806185782809625</v>
+        <v>3.806185784546269</v>
       </c>
       <c r="E7" t="n">
-        <v>1.233536460413938</v>
+        <v>1.23353646090493</v>
       </c>
       <c r="F7" t="n">
-        <v>2.109282641716446</v>
+        <v>2.109282641922523</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8242055587670627</v>
+        <v>0.8242055587327124</v>
       </c>
       <c r="H7" t="n">
-        <v>4.209301696521237</v>
+        <v>4.209301696541133</v>
       </c>
       <c r="I7" t="n">
-        <v>1.490988678325157</v>
+        <v>1.490988678326474</v>
       </c>
       <c r="J7" t="n">
-        <v>2.254351155379669</v>
+        <v>2.254351155380284</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9046698091595458</v>
+        <v>0.9046698091594937</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis Forecasting/metadata/rbfnn/validation_testing_summary.xlsx
+++ b/Thesis Forecasting/metadata/rbfnn/validation_testing_summary.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,62 +445,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>val_operational_mape</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>val_mae</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>val_rmse</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>val_r2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>test_operational_mape</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>test_mae</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>test_rmse</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>test_r2</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>evaluation_type</t>
         </is>
